--- a/data/GPS/Metricas_GPS12.xlsx
+++ b/data/GPS/Metricas_GPS12.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_79E7AF2F00E248ADEA4DC56B417C550FE97B77E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -131,25 +140,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -160,38 +170,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -199,7 +214,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -389,26 +404,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="133.25"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
+    <col min="3" max="3" width="133.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -417,21 +435,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,12 +497,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B2" s="1">
-        <v>77.833</v>
+        <v>77.832999999999998</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
@@ -492,45 +511,45 @@
         <v>19</v>
       </c>
       <c r="E2" s="1">
-        <v>6.073</v>
+        <v>6.0730000000000004</v>
       </c>
       <c r="F2" s="1">
-        <v>0.462</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="G2" s="1">
-        <v>0.088</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="H2" s="1">
-        <v>0.028</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="I2" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J2" s="1">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="L2" s="1">
-        <v>4.908</v>
+        <v>4.9080000000000004</v>
       </c>
       <c r="M2" s="1">
-        <v>-5.568</v>
+        <v>-5.5679999999999996</v>
       </c>
       <c r="N2" s="1">
-        <v>30.118</v>
+        <v>30.117999999999999</v>
       </c>
       <c r="O2" s="1">
-        <v>1292.012</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>1292.0119999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B3" s="1">
-        <v>88.017</v>
+        <v>88.016999999999996</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -542,42 +561,42 @@
         <v>6.9</v>
       </c>
       <c r="F3" s="1">
-        <v>0.743</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="G3" s="1">
-        <v>0.133</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J3" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="L3" s="1">
-        <v>4.413</v>
+        <v>4.4130000000000003</v>
       </c>
       <c r="M3" s="1">
-        <v>-4.636</v>
+        <v>-4.6360000000000001</v>
       </c>
       <c r="N3" s="1">
-        <v>28.674</v>
+        <v>28.673999999999999</v>
       </c>
       <c r="O3" s="1">
-        <v>1184.237</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>1184.2370000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B4" s="1">
-        <v>77.283</v>
+        <v>77.283000000000001</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
@@ -586,45 +605,45 @@
         <v>19</v>
       </c>
       <c r="E4" s="1">
-        <v>6.378</v>
+        <v>6.3780000000000001</v>
       </c>
       <c r="F4" s="1">
-        <v>0.658</v>
+        <v>0.65800000000000003</v>
       </c>
       <c r="G4" s="1">
         <v>0.151</v>
       </c>
       <c r="H4" s="1">
-        <v>0.032</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="I4" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="J4" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="K4" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="L4" s="1">
         <v>4.601</v>
       </c>
       <c r="M4" s="1">
-        <v>-4.511</v>
+        <v>-4.5110000000000001</v>
       </c>
       <c r="N4" s="1">
-        <v>30.924</v>
+        <v>30.923999999999999</v>
       </c>
       <c r="O4" s="1">
         <v>1114.723</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B5" s="1">
-        <v>78.167</v>
+        <v>78.167000000000002</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>23</v>
@@ -633,45 +652,45 @@
         <v>21</v>
       </c>
       <c r="E5" s="1">
-        <v>6.729</v>
+        <v>6.7290000000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>0.807</v>
+        <v>0.80700000000000005</v>
       </c>
       <c r="G5" s="1">
         <v>0.129</v>
       </c>
       <c r="H5" s="1">
-        <v>0.043</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="I5" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="J5" s="1">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="K5" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="L5" s="1">
         <v>4.827</v>
       </c>
       <c r="M5" s="1">
-        <v>-4.833</v>
+        <v>-4.8330000000000002</v>
       </c>
       <c r="N5" s="1">
-        <v>33.059</v>
+        <v>33.058999999999997</v>
       </c>
       <c r="O5" s="1">
         <v>1474.277</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B6" s="1">
-        <v>77.967</v>
+        <v>77.966999999999999</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>24</v>
@@ -680,45 +699,45 @@
         <v>19</v>
       </c>
       <c r="E6" s="1">
-        <v>5.735</v>
+        <v>5.7350000000000003</v>
       </c>
       <c r="F6" s="1">
         <v>0.318</v>
       </c>
       <c r="G6" s="1">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="H6" s="1">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="I6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J6" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="K6" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="L6" s="1">
-        <v>5.283</v>
+        <v>5.2830000000000004</v>
       </c>
       <c r="M6" s="1">
-        <v>-4.725</v>
+        <v>-4.7249999999999996</v>
       </c>
       <c r="N6" s="1">
-        <v>30.031</v>
+        <v>30.030999999999999</v>
       </c>
       <c r="O6" s="1">
         <v>1195.135</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B7" s="1">
-        <v>77.717</v>
+        <v>77.716999999999999</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>25</v>
@@ -727,45 +746,45 @@
         <v>21</v>
       </c>
       <c r="E7" s="1">
-        <v>6.155</v>
+        <v>6.1550000000000002</v>
       </c>
       <c r="F7" s="1">
-        <v>0.586</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="G7" s="1">
-        <v>0.076</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="H7" s="1">
-        <v>0.021</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="I7" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J7" s="1">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="L7" s="1">
-        <v>4.914</v>
+        <v>4.9139999999999997</v>
       </c>
       <c r="M7" s="1">
-        <v>-5.347</v>
+        <v>-5.3470000000000004</v>
       </c>
       <c r="N7" s="1">
-        <v>31.777</v>
+        <v>31.777000000000001</v>
       </c>
       <c r="O7" s="1">
-        <v>1061.101</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1061.1010000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B8" s="1">
-        <v>76.933</v>
+        <v>76.933000000000007</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>26</v>
@@ -774,45 +793,45 @@
         <v>27</v>
       </c>
       <c r="E8" s="1">
-        <v>6.371</v>
+        <v>6.3710000000000004</v>
       </c>
       <c r="F8" s="1">
-        <v>1.068</v>
+        <v>1.0680000000000001</v>
       </c>
       <c r="G8" s="1">
-        <v>0.229</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>0.052</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="I8" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="L8" s="1">
-        <v>5.348</v>
+        <v>5.3479999999999999</v>
       </c>
       <c r="M8" s="1">
         <v>-6.375</v>
       </c>
       <c r="N8" s="1">
-        <v>32.184</v>
+        <v>32.183999999999997</v>
       </c>
       <c r="O8" s="1">
-        <v>1302.551</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>1302.5509999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B9" s="1">
-        <v>83.867</v>
+        <v>83.867000000000004</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -821,28 +840,28 @@
         <v>29</v>
       </c>
       <c r="E9" s="1">
-        <v>7.164</v>
+        <v>7.1639999999999997</v>
       </c>
       <c r="F9" s="1">
-        <v>1.213</v>
+        <v>1.2130000000000001</v>
       </c>
       <c r="G9" s="1">
-        <v>0.258</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="I9" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="J9" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K9" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1">
-        <v>4.788</v>
+        <v>4.7880000000000003</v>
       </c>
       <c r="M9" s="1">
         <v>-5.258</v>
@@ -854,12 +873,12 @@
         <v>338.952</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B10" s="1">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
@@ -871,42 +890,42 @@
         <v>6.54</v>
       </c>
       <c r="F10" s="1">
-        <v>0.678</v>
+        <v>0.67800000000000005</v>
       </c>
       <c r="G10" s="1">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="H10" s="1">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="I10" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="K10" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="L10" s="1">
         <v>4.968</v>
       </c>
       <c r="M10" s="1">
-        <v>-5.377</v>
+        <v>-5.3769999999999998</v>
       </c>
       <c r="N10" s="1">
-        <v>31.889</v>
+        <v>31.888999999999999</v>
       </c>
       <c r="O10" s="1">
-        <v>1659.773</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1659.7729999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B11" s="1">
-        <v>78.683</v>
+        <v>78.683000000000007</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -915,28 +934,28 @@
         <v>31</v>
       </c>
       <c r="E11" s="1">
-        <v>5.995</v>
+        <v>5.9950000000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>0.619</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="G11" s="1">
         <v>0.104</v>
       </c>
       <c r="H11" s="1">
-        <v>0.021</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="I11" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="K11" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="L11" s="1">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="M11" s="1">
         <v>-6.633</v>
@@ -948,12 +967,12 @@
         <v>959.596</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B12" s="1">
-        <v>75.883</v>
+        <v>75.882999999999996</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>33</v>
@@ -962,7 +981,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="1">
-        <v>6.519</v>
+        <v>6.5190000000000001</v>
       </c>
       <c r="F12" s="1">
         <v>1.077</v>
@@ -971,22 +990,22 @@
         <v>0.193</v>
       </c>
       <c r="H12" s="1">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I12" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J12" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="K12" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="L12" s="1">
-        <v>4.943</v>
+        <v>4.9429999999999996</v>
       </c>
       <c r="M12" s="1">
-        <v>-6.341</v>
+        <v>-6.3410000000000002</v>
       </c>
       <c r="N12" s="1">
         <v>31.331</v>
@@ -995,12 +1014,12 @@
         <v>1406.88</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B13" s="1">
-        <v>76.533</v>
+        <v>76.533000000000001</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>34</v>
@@ -1009,45 +1028,45 @@
         <v>29</v>
       </c>
       <c r="E13" s="1">
-        <v>6.503</v>
+        <v>6.5030000000000001</v>
       </c>
       <c r="F13" s="1">
-        <v>0.981</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="G13" s="1">
         <v>0.153</v>
       </c>
       <c r="H13" s="1">
-        <v>0.055</v>
+        <v>5.5E-2</v>
       </c>
       <c r="I13" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="J13" s="1">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="K13" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="L13" s="1">
-        <v>4.861</v>
+        <v>4.8609999999999998</v>
       </c>
       <c r="M13" s="1">
-        <v>-4.999</v>
+        <v>-4.9989999999999997</v>
       </c>
       <c r="N13" s="1">
-        <v>32.324</v>
+        <v>32.323999999999998</v>
       </c>
       <c r="O13" s="1">
         <v>1092.867</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B14" s="1">
-        <v>77.967</v>
+        <v>77.966999999999999</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>35</v>
@@ -1056,45 +1075,45 @@
         <v>36</v>
       </c>
       <c r="E14" s="1">
-        <v>6.265</v>
+        <v>6.2649999999999997</v>
       </c>
       <c r="F14" s="1">
-        <v>0.854</v>
+        <v>0.85399999999999998</v>
       </c>
       <c r="G14" s="1">
         <v>0.127</v>
       </c>
       <c r="H14" s="1">
-        <v>0.028</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="I14" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J14" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K14" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="L14" s="1">
-        <v>4.438</v>
+        <v>4.4379999999999997</v>
       </c>
       <c r="M14" s="1">
-        <v>-4.858</v>
+        <v>-4.8579999999999997</v>
       </c>
       <c r="N14" s="1">
-        <v>30.704</v>
+        <v>30.704000000000001</v>
       </c>
       <c r="O14" s="1">
-        <v>1253.228</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>1253.2280000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="B15" s="1">
-        <v>82.517</v>
+        <v>82.516999999999996</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>37</v>
@@ -1103,40 +1122,40 @@
         <v>31</v>
       </c>
       <c r="E15" s="1">
-        <v>6.917</v>
+        <v>6.9169999999999998</v>
       </c>
       <c r="F15" s="1">
         <v>0.9</v>
       </c>
       <c r="G15" s="1">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="I15" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J15" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="K15" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="L15" s="1">
-        <v>4.511</v>
+        <v>4.5110000000000001</v>
       </c>
       <c r="M15" s="1">
-        <v>-5.368</v>
+        <v>-5.3680000000000003</v>
       </c>
       <c r="N15" s="1">
-        <v>29.804</v>
+        <v>29.803999999999998</v>
       </c>
       <c r="O15" s="1">
-        <v>1314.994</v>
+        <v>1314.9939999999999</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>